--- a/planillas/consolidado.xlsx
+++ b/planillas/consolidado.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH79"/>
+  <dimension ref="A1:AH165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8140,6 +8140,8294 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>25/06/2024 al 05/07/2024</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>124 A 6 M 5 D</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Aguirre genesis Milagro</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>57355675</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Mision Sachapera Tartagal</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>43377</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>5 A 9 M 1 D</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1650</v>
+      </c>
+      <c r="L82" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>40</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>45432</v>
+      </c>
+      <c r="O82" t="n">
+        <v>9040</v>
+      </c>
+      <c r="P82" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="R82" t="n">
+        <v>-5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="V82" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="W82" t="n">
+        <v>86</v>
+      </c>
+      <c r="X82" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Aguire zulemaP Patricia</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica Reagudizada - Sindrome genetico  Cornelia de Lange - Trastornos deglutorios </t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA EN TTO SINDROME GENETICO TRASTORNO DEGLUTORIO </t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA NUTRILON PEPTY JR HE 180CC /TOMA AL 18% 6 TOMAS </t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Rasputin Mendoza Luciana Sara</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica </t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>59812431</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Jerusalem y Mateo Mision Cherenta Tartagal</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Pediatria 1° Piso</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>44972</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1 A 4 M 20 D</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>35</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>45435</v>
+      </c>
+      <c r="O83" t="n">
+        <v>6640</v>
+      </c>
+      <c r="P83" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="R83" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="S83" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="U83" s="2" t="n">
+        <v>45477</v>
+      </c>
+      <c r="V83" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="W83" t="n">
+        <v>75</v>
+      </c>
+      <c r="X83" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>Rasputin Florencia Carla</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>GEA con Deshidratacion severa-DNT cronica Reagudizada -IRA-Trastornos del medio Inerno</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>RECUPERADA NUTRICIONALMENTE , CELIAQUIA Y APLV E/E</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LECHE 0% LACTOSA EN FORMA DE PREPARACIONES </t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>lucas Beatriz Hermelida</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SNG </t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>59711607</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monte Sinai Salvador Mazzas pocitos </t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>44916</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1 A 6 M 14 D</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>3.070</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>46</v>
+      </c>
+      <c r="M84" t="n">
+        <v>39</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>45441</v>
+      </c>
+      <c r="O84" t="n">
+        <v>6600</v>
+      </c>
+      <c r="P84" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="R84" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="S84" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="U84" s="2" t="n">
+        <v>45471</v>
+      </c>
+      <c r="V84" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="W84" t="n">
+        <v>73</v>
+      </c>
+      <c r="X84" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>Sanchez Beatriz</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica agudizada calorica proteica moderada </t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>DNT CRONICA EN TTO</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula Entera v.o 150cc/toma al 15% </t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Suarez josefina Isabella</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica </t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>cornejo</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45295</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>50</v>
+      </c>
+      <c r="M85" t="n">
+        <v>39</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>45450</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P85" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="U85" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="V85" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="W85" t="n">
+        <v>58</v>
+      </c>
+      <c r="X85" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milagros Isabelina </t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>DNTcronica calorica moderada- scabiosis- anemia cronica-ARS</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>FORMULA DE INICIO 690CC AL 18% CADA 3HS V.O</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gonzalez Luis Antonio </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>70198574</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MISION LA PAZ SVE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTI PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45409</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2,85</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>48</v>
+      </c>
+      <c r="M86" t="n">
+        <v>37</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>45462</v>
+      </c>
+      <c r="O86" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P86" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="R86" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gonzalez Nilda </t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica calorica proteica severasecundaria- Cardiopatia congenita- sindrome genetico e/e </t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 60cc/toma al 18% cada 3hs </t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Arias Mia Rocio</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT aguda calorica </t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>70298049</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SAN SILVESTRE TARTAGAL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45398</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2,780</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>50</v>
+      </c>
+      <c r="M87" t="n">
+        <v>42</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O87" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="P87" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="R87" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="S87" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moreno Angela </t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>DNT Aguda Calorica primaria- Impetigo- ARS</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Continua Internada</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>formula de inicio</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isquica Martina </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dnt cronica </t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>70197551</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>B LA MERCED MOSCONI</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45310</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>49</v>
+      </c>
+      <c r="M88" t="n">
+        <v>38</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="P88" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="R88" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="S88" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Villareal Silvia </t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT Aguda Calorica Moderada - Retraso del Neurodesarrollo -Microcefalia-Quiste simple Hepatico- Trastorno Deglutorio en estudio </t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>Continua Internada</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio </t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Torres Licet Maria Cristina </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>70298124</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F </t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M LA MORA TARTAGAL </t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45428</v>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>45</v>
+      </c>
+      <c r="M89" t="n">
+        <v>35</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O89" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="P89" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="R89" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U89" s="2" t="n">
+        <v>45477</v>
+      </c>
+      <c r="V89" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="W89" t="n">
+        <v>50</v>
+      </c>
+      <c r="X89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Torres Florencia</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT Proteico Calorica </t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 65CC 7TOMA AL 18% CADA 3HS </t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarraga Agustiba Mrtina </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>70039361</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F </t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>B 9 DE JULIO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>3,04</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>39</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="O90" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="P90" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="R90" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="S90" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarraga Eliana </t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>DNT cronica calorica proteica moderada- anemia cronica- bronqueolitis leve - ars</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula 0% lactosa 120cc/toma al 15% por sng </t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segundo Yanet Joselin </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>59428115</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M WHICHI MOSCONI </t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Pediatria 1° Piso</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>44721</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>44</v>
+      </c>
+      <c r="M91" t="n">
+        <v>37</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="O91" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="P91" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R91" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="S91" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA ARMONICA. ANEMIA CRONICA, TBC A ESTUDIAR, ARS</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula 0% lactosa 200cc/toma al 15% por sng </t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>125 A 0 M 8 D</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JUSTINIANO CELESTE  ABIGAIL</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>70298051</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLA SAVEDRA </t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" s="2" t="n">
+        <v>45636</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P94" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="R94" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="S94" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="T94" t="n">
+        <v>78</v>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>JUSTINIANO MELANI</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>DNT CRONICA SECUNDARIA, DIARREA INTERMITENTE, JUDICIALIZADA, RETRASO DE PAUTAS MADURATIVAS,ARS</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>CRIOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ORQUIZO NICOLE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>70198781</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>PASE DE SALA PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L95" t="n">
+        <v>40</v>
+      </c>
+      <c r="M95" t="n">
+        <v>34</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>45644</v>
+      </c>
+      <c r="O95" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="P95" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>P 10</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>73</v>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORQUIZO MARCELA </t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>ECNE, DISPLASIA BRONCOPULMONAR, GASTROTOMIA, RGE SEVERO, DESNUTRICIÓN CRÓNICA MODERADA
+2RIA,TRASTORNOS DEGLUTORIOS, ARS</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>CHOROTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ HEBER </t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>59406296</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASE DE SLA DE PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>44912</v>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>50</v>
+      </c>
+      <c r="M96" t="n">
+        <v>40</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>45649</v>
+      </c>
+      <c r="O96" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P96" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="R96" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="T96" t="n">
+        <v>66</v>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>DELMA SOLIZ</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MARASMO KWASHIORKOR, TRASTORNOS METABOLICOS, ANEMIA SEVERA, GEA EN RESOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>INTERNADO</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABRAHAM MARIANELA ROSA </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>59288702</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DERIVACION APS MOSCONI</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>44936</v>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" s="2" t="n">
+        <v>45649</v>
+      </c>
+      <c r="O97" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P97" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="S97" t="n">
+        <v>-247</v>
+      </c>
+      <c r="T97" t="n">
+        <v>90</v>
+      </c>
+      <c r="U97" s="2" t="n">
+        <v>45664</v>
+      </c>
+      <c r="V97" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="W97" t="n">
+        <v>81</v>
+      </c>
+      <c r="X97" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>92</v>
+      </c>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>ABRAHAM ROXANA (TIA)</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA CALORICA PROTEICA MODERADA, GEA EN REOLUCION, ARS</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>RECUPERADA NUTRICIONALMENTE INTOLERANCIA A LA LACTOSA TRANSITORIA</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA ENTERA 0% LACTOSA 200CC/TOMA AL 15% VIA ORAL </t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BURGOS MARILINA </t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DNT AGUDA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>59990369</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>LAPACHO II</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CONSULTORIO EXTERNO</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>45128</v>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L98" t="n">
+        <v>50</v>
+      </c>
+      <c r="M98" t="n">
+        <v>40</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>45652</v>
+      </c>
+      <c r="O98" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="P98" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="R98" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="S98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>82</v>
+      </c>
+      <c r="U98" s="2" t="n">
+        <v>45660</v>
+      </c>
+      <c r="V98" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="W98" t="n">
+        <v>77</v>
+      </c>
+      <c r="X98" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BURGOS CLAUDIA </t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>DESNUTRICION AGUDA CALORICA MODERADA, GEA. ALT MB CON HIPOPOTASEMIA SEVERA,IRA, ANEMIA CRONICA,ARS</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>RECUPERADA NUTRICIONALMENTE</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>FORMULA ENTERA 200 CC/TOMA AL 15% VIA ORAL</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MAMANI YESENIA ZAMIRA VIVIANA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V. O </t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>59866527</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDOATRIA</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="L99" t="n">
+        <v>50</v>
+      </c>
+      <c r="M99" t="n">
+        <v>39</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>45659</v>
+      </c>
+      <c r="O99" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="P99" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="R99" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="S99" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="T99" t="n">
+        <v>91</v>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>MAMANI GABRIELA</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA LEVE, ANEMIA CRONICA, DIARREA CRONICA</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADA </t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHICHI </t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BASUALDO SAMUEL LUCINDO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>59760021</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>PASE HOSPITAL ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>45275</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L100" t="n">
+        <v>48</v>
+      </c>
+      <c r="M100" t="n">
+        <v>39</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O100" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P100" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="R100" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="S100" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="T100" t="n">
+        <v>77</v>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA BEATRIZ </t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, ARS</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADO </t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS IRIS </t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SIN DNI</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>44756</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L101" t="n">
+        <v>44</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O101" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="P101" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="R101" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="T101" t="n">
+        <v>86</v>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>CEBALLOS MARILINA</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA MODERADA, TRASTORNOS METABOLICOS EN RESOLUCIÓN, GEA EN RESOLUCIÓN,</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>17//08/2024   al 23/08/2024</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>124 A 7 M 23 D</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gonzalez Luis Antonio </t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>70198574</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Mision La Paz Santa Victoria Este</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTI PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>45409</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0 A 3 M 27 D</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="L104" t="n">
+        <v>48</v>
+      </c>
+      <c r="M104" t="n">
+        <v>37</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>45462</v>
+      </c>
+      <c r="O104" t="n">
+        <v>2600</v>
+      </c>
+      <c r="P104" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="R104" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="S104" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U104" s="2" t="n">
+        <v>45524</v>
+      </c>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gonzalez Nilda </t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica calorica proteica severasecundaria- Cardiopatia congenita- sindrome genetico e/e </t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 60cc/toma al 18% cada 3hs </t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>criollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Burgos Marilina Roberta Paola</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT aguda </t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>59990369</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Mision Lapacho II Tartagal</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>45128</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1 A 1 M 2 D</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L105" t="n">
+        <v>50</v>
+      </c>
+      <c r="M105" t="n">
+        <v>40</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>45488</v>
+      </c>
+      <c r="O105" t="n">
+        <v>7580</v>
+      </c>
+      <c r="P105" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R105" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="S105" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="U105" s="2" t="n">
+        <v>45509</v>
+      </c>
+      <c r="V105" t="n">
+        <v>8660</v>
+      </c>
+      <c r="W105" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="X105" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>Ceballo Claudia</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>DNT Aguda Calorica Moderada -GEA- Alto Riesgo social</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>Dsnutricion Calorica proteica Leve</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Formula de leche entera 0% lactosa via enteral + leche materna</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Lopez Herrera Roman Armando</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>via oral</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>59938743</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Mision Km 6 Tartagal</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1 A 1 M 24 D</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>3250</v>
+      </c>
+      <c r="L106" t="n">
+        <v>48</v>
+      </c>
+      <c r="M106" t="n">
+        <v>39</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>45503</v>
+      </c>
+      <c r="O106" t="n">
+        <v>7400</v>
+      </c>
+      <c r="P106" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="U106" s="2" t="n">
+        <v>45526</v>
+      </c>
+      <c r="V106" t="n">
+        <v>8980</v>
+      </c>
+      <c r="W106" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="X106" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herrera Sandra </t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>DNT cronica calorica leve - IRAB-Anemia cronica- Enteroparasitosis con antecedentes  de PNT/AEG</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>Bronquitis Aguda debidoa un virus Sincitial Respiratorio</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula Leche entera 15% + azucar4% 200cc x 5 tomas /diarias + dieta hipercalorica noroproeica con colaciones </t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Arce Fernanda sisiana Rosaly</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>59813347</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Paraje TONONO Tartagal</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Pediatria 1° Piso Tartagal</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1 A 5 M 13 D</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" t="n">
+        <v>48</v>
+      </c>
+      <c r="M107" t="n">
+        <v>40</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>45509</v>
+      </c>
+      <c r="O107" t="n">
+        <v>7690</v>
+      </c>
+      <c r="P107" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="R107" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="S107" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>Arce Dina Rebeca</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>DNT croncia Calorica Pediatrica Leve - Anemia Moderada Alto RiesgoSocial</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretario Dana Veronica </t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica </t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>59759459</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Comunidad Pablo Secretario Tartagal</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ConsultoriosExternos</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>44951</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>1 A 6 M 29 D</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="L108" t="n">
+        <v>49</v>
+      </c>
+      <c r="M108" t="n">
+        <v>41</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>45510</v>
+      </c>
+      <c r="O108" t="n">
+        <v>7890</v>
+      </c>
+      <c r="P108" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="R108" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="S108" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U108" s="2" t="n">
+        <v>45527</v>
+      </c>
+      <c r="V108" t="n">
+        <v>9440</v>
+      </c>
+      <c r="W108" t="n">
+        <v>75</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>1555</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>Perez Esilda</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>DNT cronica  Calorica Proteica leve - Diarrea Intrmitente - Pio dermititis - Alto Rieso Social</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>Bronquioliti aguda no especificada Recuperada Nutricional</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula de leche entera 0%  lactossa + dieta astringente </t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Gerez eda Lucia</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT aguda </t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>70096673</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Mision km 6 tartagal</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>0 A 9 M 7 D</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L109" t="n">
+        <v>51</v>
+      </c>
+      <c r="M109" t="n">
+        <v>39</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>45513</v>
+      </c>
+      <c r="O109" t="n">
+        <v>6500</v>
+      </c>
+      <c r="P109" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S109" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soruco Eliana </t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>DNT aguda calorica - Anemia- cronica -IRAB-Alto Riesgo Social</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>Continua Internada</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Gavi Adolfo Belarde</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DNTcronica</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>via oral</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>59760007</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alto La sierra Dpto Rivadavia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Pediatria 1° Piso Tartagal</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>45128</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>1 A 1 M 2 D</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L110" t="n">
+        <v>43</v>
+      </c>
+      <c r="M110" t="n">
+        <v>36</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>45511</v>
+      </c>
+      <c r="O110" t="n">
+        <v>7890</v>
+      </c>
+      <c r="P110" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="R110" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="S110" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="U110" s="2" t="n">
+        <v>45517</v>
+      </c>
+      <c r="V110" t="n">
+        <v>8250</v>
+      </c>
+      <c r="W110" t="n">
+        <v>79</v>
+      </c>
+      <c r="X110" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>360</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suarez Beatriz </t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica Calorica Leve - Anemia Cronica -GEA Trastornos del Medio Interno </t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>DNT Proteica Calorica Leve</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula de leche Entera al 15% ´azucar 4% 200cc x 5/T/diarias + dieta hipercalorica monoproteica c/ colaciones </t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Peña Luis Leonardo</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica  </t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>589288719</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Mision El Cruce General Enrique Mosconi</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>45053</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1 A 3 M 16 D</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L111" t="n">
+        <v>48</v>
+      </c>
+      <c r="M111" t="n">
+        <v>40</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>45519</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>.6.920</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>705</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="R111" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="S111" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>Bravo Milagro soldad</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NICASIO Victoria Arminda</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica  </t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>59989750</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Mision Km 7 tartagal</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>45094</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>1 A 2 M 6 D</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L112" t="n">
+        <v>47</v>
+      </c>
+      <c r="M112" t="n">
+        <v>39</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>45523</v>
+      </c>
+      <c r="O112" t="n">
+        <v>7020</v>
+      </c>
+      <c r="P112" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="R112" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="S112" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastor Benigna </t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica Caorica Proteica </t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>7</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GONZALEZ  Luis Antonio</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SGN</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>70198574</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Mision La Paz Santa Victoria Este</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>HPMI Salta</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>45409</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>0 A 3 M 27 D</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="L113" t="n">
+        <v>48</v>
+      </c>
+      <c r="M113" t="n">
+        <v>37</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>45526</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Formula de inicioal 18% 70cc cada 3 hs x 8 tomas mas lactancia materna</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>wichi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>05/07/2024 al 12/07/2024</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>124 A 6 M 12 D</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gonzalez Luis Antonio </t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DNT cronica</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>70198574</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>MISION LA PAZ SVE</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTI PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>45409</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2,85</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>48</v>
+      </c>
+      <c r="M116" t="n">
+        <v>37</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>45462</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P116" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="R116" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="S116" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gonzalez Nilda </t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT cronica calorica proteica severasecundaria- Cardiopatia congenita- sindrome genetico e/e </t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>Continua Internado</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 60cc/toma al 18% cada 3hs </t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Arias Mia Rocio</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT aguda calorica </t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>70298049</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SAN SILVESTRE TARTAGAL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>45398</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2,780</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>50</v>
+      </c>
+      <c r="M117" t="n">
+        <v>42</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O117" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="P117" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="R117" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="S117" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U117" s="2" t="n">
+        <v>45481</v>
+      </c>
+      <c r="V117" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="W117" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="X117" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moreno Angela </t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>DNT Aguda Calorica primaria- Impetigo- ARS</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio 90 CC /TOMA AL 18% POR SUCCION </t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isquica Martina </t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dnt cronica </t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>70197551</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>B LA MERCED MOSCONI</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>45310</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>49</v>
+      </c>
+      <c r="M118" t="n">
+        <v>38</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="O118" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="P118" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="R118" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="S118" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Villareal Silvia </t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT Aguda Calorica Moderada - Retraso del Neurodesarrollo -Microcefalia-Quiste simple Hepatico- Trastorno Deglutorio en estudio </t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>Continua Internada</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula de inicio </t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarraga Agustiba Mrtina </t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>70039361</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F </t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>B 9 DE JULIO</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>3,04</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="M119" t="n">
+        <v>39</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="O119" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="P119" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="R119" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="S119" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarraga Eliana </t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>DNT cronica calorica proteica moderada- anemia cronica- bronqueolitis leve - ars</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula 0% lactosa 120cc/toma al 15% por sng </t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segundo Yanet Joselin </t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>59428115</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M WHICHI MOSCONI </t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Pediatria 1° Piso</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>44721</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>44</v>
+      </c>
+      <c r="M120" t="n">
+        <v>37</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="O120" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="S120" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA ARMONICA. ANEMIA CRONICA, TBC A ESTUDIAR, ARS</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">formula 0% lactosa 200cc/toma al 15% por sng </t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diaz Yeimi Irene </t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>59938632</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>M EL CRUCE MOSCONI</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Consultorios Externos</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>44715</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>3,09</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M121" t="n">
+        <v>37</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>45481</v>
+      </c>
+      <c r="O121" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P121" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>Romero Adriana</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>Desnutricon Cronica Calorica secundaria - Trastorno deglutorio - ecne - RMG -SBOR</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continua internada </t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>formula de inicio</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>125 A 0 M 15 D</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>JUSTINIANO CELESTE  ABIGAIL</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>70298051</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLA SAVEDRA </t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" s="2" t="n">
+        <v>45636</v>
+      </c>
+      <c r="O124" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P124" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="S124" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="T124" t="n">
+        <v>78</v>
+      </c>
+      <c r="U124" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="V124" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W124" t="n">
+        <v>64</v>
+      </c>
+      <c r="X124" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>96</v>
+      </c>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>HOGAR DE NIÑOS JUDICIALIZADA</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>DNT CRONICA SECUNDARIA, DIARREA INTERMITENTE, JUDICIALIZADA, RETRASO DE PAUTAS MADURATIVAS,ARS</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA 0% LACTOSA 150CC/TOMA V.O </t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>CRIOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ORQUIZO NICOLE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>70198781</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>PASE DE SALA PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L125" t="n">
+        <v>40</v>
+      </c>
+      <c r="M125" t="n">
+        <v>34</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>45644</v>
+      </c>
+      <c r="O125" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="P125" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>P 10</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>73</v>
+      </c>
+      <c r="U125" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="V125" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="W125" t="n">
+        <v>64</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>P 25  50</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>P 10   25</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="AA125" t="n">
+        <v>84</v>
+      </c>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORQUIZO MARCELA </t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>ECNE, DISPLASIA BRONCOPULMONAR, GASTROTOMIA, RGE SEVERO, DESNUTRICIÓN CRÓNICA MODERADA
+2RIA,TRASTORNOS DEGLUTORIOS, ARS</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DESNUTRICION CRONICA EN RECUPERACION </t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA DE INICIO 140CC/TOMA AL 22% 6 TOMAS /D SNG </t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>CHOROTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ HEBER </t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>59406296</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASE DE SLA DE PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>44912</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>50</v>
+      </c>
+      <c r="M126" t="n">
+        <v>40</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>45649</v>
+      </c>
+      <c r="O126" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P126" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="S126" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="T126" t="n">
+        <v>66</v>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>DELMA SOLIZ</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MARASMO KWASHIORKOR, TRASTORNOS METABOLICOS, ANEMIA SEVERA, GEA EN RESOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>INTERNADO</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>MAMANI YESENIA ZAMIRA VIVIANA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V. O </t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>59866527</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDOATRIA</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="L127" t="n">
+        <v>50</v>
+      </c>
+      <c r="M127" t="n">
+        <v>39</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>45659</v>
+      </c>
+      <c r="O127" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="P127" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="T127" t="n">
+        <v>91</v>
+      </c>
+      <c r="U127" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="V127" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="W127" t="n">
+        <v>78</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>MAMANI GABRIELA</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA LEVE, ANEMIA CRONICA, DIARREA CRONICA</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>RECUPERADA NUTRICIONALMENTE INTOLERANCIA A LA LACTOSA TRANSITORIA</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMUAL ENTERA 0% LACTOSA 200C/TOMA AL 15% V.O </t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHICHI </t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BASUALDO SAMUEL LUCINDO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>59760021</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>PASE HOSPITAL ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>45275</v>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L128" t="n">
+        <v>48</v>
+      </c>
+      <c r="M128" t="n">
+        <v>39</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O128" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P128" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="R128" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="S128" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="T128" t="n">
+        <v>77</v>
+      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA BEATRIZ </t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, ARS</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADO </t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS IRIS </t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SIN DNI</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>44756</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L129" t="n">
+        <v>44</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O129" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="R129" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="S129" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="T129" t="n">
+        <v>86</v>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>CEBALLOS MARILINA</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA MODERADA, TRASTORNOS METABOLICOS EN RESOLUCIÓN, GEA EN RESOLUCIÓN,</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GEREZ EDA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>70096073</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>KM6</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L130" t="n">
+        <v>51</v>
+      </c>
+      <c r="M130" t="n">
+        <v>39</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>45664</v>
+      </c>
+      <c r="O130" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P130" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S130" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="T130" t="n">
+        <v>71</v>
+      </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>SORUCO ELIANA</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICION CRONICA REAGUDIZADA MODERADA A SEVERA, IRA, ARS, DIARREA, HERNIA UMBILICAL REDUCTIBLE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DIAZ ESTRELLA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DNT  CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>59990421</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>KM6</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>45145</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L131" t="n">
+        <v>50</v>
+      </c>
+      <c r="M131" t="n">
+        <v>40</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="O131" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="P131" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="R131" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="S131" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="T131" t="n">
+        <v>81</v>
+      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>SORUCO TAMARA</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA, IRA, DIARREA , ARS</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ZABALA GERARDO</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DNT RONICA REAG</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>70227354</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>KM 6</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>45341</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L132" t="n">
+        <v>49</v>
+      </c>
+      <c r="M132" t="n">
+        <v>39</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="O132" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="P132" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="R132" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="S132" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="T132" t="n">
+        <v>78</v>
+      </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERRERA SANDRA </t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, DIARREAS INTERMITENTES</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADO </t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>FORMULA INDICADA EN INTRNACION F100</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TORRES CATALEA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>59236043</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>PASE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>44573</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L133" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M133" t="n">
+        <v>39</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>45672</v>
+      </c>
+      <c r="O133" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>IMC 12,4 -2,7</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T133" t="n">
+        <v>75</v>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES LOIDA </t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA CALORICA PROTEICA MODERADA A SEVERA, DESEQUILIBRIO DEL MEDIO INTERNO, ANEMIA MODERADA, DIARREA INTERMITENTE </t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>125 A 0 M 22 D</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ HEBER </t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>59406296</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASE DE SLA DE PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>44912</v>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L136" t="n">
+        <v>50</v>
+      </c>
+      <c r="M136" t="n">
+        <v>40</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>45649</v>
+      </c>
+      <c r="O136" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P136" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="T136" t="n">
+        <v>66</v>
+      </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>DELMA SOLIZ</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MARASMO KWASHIORKOR, TRASTORNOS METABOLICOS, ANEMIA SEVERA, GEA EN RESOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>INTERNADO</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BASUALDO SAMUEL LUCINDO</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>59760021</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>PASE HOSPITAL ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>45275</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L137" t="n">
+        <v>48</v>
+      </c>
+      <c r="M137" t="n">
+        <v>39</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O137" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P137" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="T137" t="n">
+        <v>77</v>
+      </c>
+      <c r="U137" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="V137" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="W137" t="n">
+        <v>72</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>92</v>
+      </c>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA BEATRIZ </t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, ARS</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS IRIS </t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>SIN DNI</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>44756</v>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L138" t="n">
+        <v>44</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O138" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="P138" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="T138" t="n">
+        <v>86</v>
+      </c>
+      <c r="U138" s="2" t="n">
+        <v>45313</v>
+      </c>
+      <c r="V138" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="W138" t="n">
+        <v>79</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>CEBALLOS MARILINA</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA MODERADA, TRASTORNOS METABOLICOS EN RESOLUCIÓN, GEA EN RESOLUCIÓN,</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>RECUPERADA NURICIONALMENTE</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GEREZ EDA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>70096073</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>KM6</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L139" t="n">
+        <v>51</v>
+      </c>
+      <c r="M139" t="n">
+        <v>39</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>45664</v>
+      </c>
+      <c r="O139" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P139" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="R139" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S139" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="T139" t="n">
+        <v>71</v>
+      </c>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>SORUCO ELIANA</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICION CRONICA REAGUDIZADA MODERADA A SEVERA, IRA, ARS, DIARREA, HERNIA UMBILICAL REDUCTIBLE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>DIAZ ESTRELLA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DNT  CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>59990421</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>KM6</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>45145</v>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L140" t="n">
+        <v>50</v>
+      </c>
+      <c r="M140" t="n">
+        <v>40</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="P140" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="R140" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="S140" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="T140" t="n">
+        <v>81</v>
+      </c>
+      <c r="U140" s="2" t="n">
+        <v>45677</v>
+      </c>
+      <c r="V140" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="W140" t="n">
+        <v>74</v>
+      </c>
+      <c r="X140" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>SORUCO TAMARA</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA, IRA, DIARREA , ARS</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ZABALA GERARDO</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DNT RONICA REAG</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>70227354</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>KM 6</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>45341</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L141" t="n">
+        <v>49</v>
+      </c>
+      <c r="M141" t="n">
+        <v>39</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="O141" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="P141" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="R141" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="T141" t="n">
+        <v>78</v>
+      </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERRERA SANDRA </t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, DIARREAS INTERMITENTES</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADO </t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>FORMULA INDICADA EN INTRNACION F100</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TORRES CATALEA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>59236043</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>PASE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>44573</v>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L142" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M142" t="n">
+        <v>39</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>45672</v>
+      </c>
+      <c r="O142" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>IMC 12,4 -2,7</t>
+        </is>
+      </c>
+      <c r="R142" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="S142" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T142" t="n">
+        <v>75</v>
+      </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES LOIDA </t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA CALORICA PROTEICA MODERADA A SEVERA, DESEQUILIBRIO DEL MEDIO INTERNO, ANEMIA MODERADA, DIARREA INTERMITENTE </t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS PATRICIA </t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DNT CRONCA REAG</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>70164487</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PACARA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PDIATRIA</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>45279</v>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L143" t="n">
+        <v>45</v>
+      </c>
+      <c r="M143" t="n">
+        <v>39</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>45674</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>7 ( PESO SECO)</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="R143" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="S143" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="T143" t="n">
+        <v>81</v>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>TORRES SILVIA</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN MARASMO KWASHIORKOR, ANEMIA CRÓNICA, GEA Y TRASTORNOS DEL MEDIO INTERNO EN RESOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>FORMULA INDICCADA EN INTERNACION F100</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUELLAR RICARDO ROMERO JUNIOR </t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>70227496</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SALVADOR MAZZA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L144" t="n">
+        <v>49</v>
+      </c>
+      <c r="M144" t="n">
+        <v>40</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="O144" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="P144" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="R144" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="S144" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="T144" t="n">
+        <v>74</v>
+      </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>ROMERO ELENA</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>DESNTRICION CRONICA REAGUDIZADA  SOSPECHA DE ABANDONO (MALTRATO INFANITIL) IRAB ARS</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>FORMUAL INDICADA EN INTERNACION F100</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ TORRES MARIA LUCIA </t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>70096596</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA MORA </t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>45235</v>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L145" t="n">
+        <v>49</v>
+      </c>
+      <c r="M145" t="n">
+        <v>38</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="O145" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P145" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="R145" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="S145" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="T145" t="n">
+        <v>78</v>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORES LUCIA </t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA CALORICA MODERADA, GEA, ANEMIA CRONICA</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNDA </t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>FORMLA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHICHI </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>125 A 0 M 22 D</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ HEBER </t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DNT CRONICA</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>59406296</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>MOSCONI</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASE DE SLA DE PEDIATRIA </t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>44912</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L148" t="n">
+        <v>50</v>
+      </c>
+      <c r="M148" t="n">
+        <v>40</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>45649</v>
+      </c>
+      <c r="O148" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P148" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="R148" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="S148" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="T148" t="n">
+        <v>66</v>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>DELMA SOLIZ</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MARASMO KWASHIORKOR, TRASTORNOS METABOLICOS, ANEMIA SEVERA, GEA EN RESOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>INTERNADO</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BASUALDO SAMUEL LUCINDO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>59760021</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>PASE HOSPITAL ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>45275</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L149" t="n">
+        <v>48</v>
+      </c>
+      <c r="M149" t="n">
+        <v>39</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O149" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="P149" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="R149" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="S149" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="T149" t="n">
+        <v>77</v>
+      </c>
+      <c r="U149" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="V149" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="W149" t="n">
+        <v>72</v>
+      </c>
+      <c r="X149" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>92</v>
+      </c>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA BEATRIZ </t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, ARS</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS IRIS </t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>SIN DNI</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>44756</v>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L150" t="n">
+        <v>44</v>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" s="2" t="n">
+        <v>45665</v>
+      </c>
+      <c r="O150" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="P150" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="R150" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="S150" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="T150" t="n">
+        <v>86</v>
+      </c>
+      <c r="U150" s="2" t="n">
+        <v>45313</v>
+      </c>
+      <c r="V150" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="W150" t="n">
+        <v>79</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>CEBALLOS MARILINA</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA MODERADA, TRASTORNOS METABOLICOS EN RESOLUCIÓN, GEA EN RESOLUCIÓN,</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>RECUPERADA NURICIONALMENTE</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>GEREZ EDA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>70096073</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>KM6</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>45246</v>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L151" t="n">
+        <v>51</v>
+      </c>
+      <c r="M151" t="n">
+        <v>39</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>45664</v>
+      </c>
+      <c r="O151" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P151" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="R151" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S151" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="T151" t="n">
+        <v>71</v>
+      </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>SORUCO ELIANA</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICION CRONICA REAGUDIZADA MODERADA A SEVERA, IRA, ARS, DIARREA, HERNIA UMBILICAL REDUCTIBLE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DIAZ ESTRELLA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DNT  CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>59990421</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>KM6</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>45145</v>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L152" t="n">
+        <v>50</v>
+      </c>
+      <c r="M152" t="n">
+        <v>40</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="O152" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="P152" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="R152" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="S152" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="T152" t="n">
+        <v>81</v>
+      </c>
+      <c r="U152" s="2" t="n">
+        <v>45677</v>
+      </c>
+      <c r="V152" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="W152" t="n">
+        <v>74</v>
+      </c>
+      <c r="X152" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>SORUCO TAMARA</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA REAGUDIZADA, IRA, DIARREA , ARS</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADA NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ZABALA GERARDO</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DNT RONICA REAG</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>70227354</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>KM 6</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>DERIVACION APS</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>45341</v>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L153" t="n">
+        <v>49</v>
+      </c>
+      <c r="M153" t="n">
+        <v>39</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="O153" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="P153" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="R153" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="S153" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="T153" t="n">
+        <v>78</v>
+      </c>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERRERA SANDRA </t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN CRÓNICA MODERADA REAGUDIZADA, DIARREAS INTERMITENTES</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADO </t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>FORMULA INDICADA EN INTRNACION F100</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TORRES CATALEA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>59236043</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>PASE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>44573</v>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L154" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M154" t="n">
+        <v>39</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>45672</v>
+      </c>
+      <c r="O154" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="P154" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>IMC 12,4 -2,7</t>
+        </is>
+      </c>
+      <c r="R154" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="S154" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T154" t="n">
+        <v>75</v>
+      </c>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES LOIDA </t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CRÓNICA CALORICA PROTEICA MODERADA A SEVERA, DESEQUILIBRIO DEL MEDIO INTERNO, ANEMIA MODERADA, DIARREA INTERMITENTE </t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA INDICADA EN INTERNACION F100 </t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS PATRICIA </t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DNT CRONCA REAG</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>70164487</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>PACARA</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PDIATRIA</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>45279</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L155" t="n">
+        <v>45</v>
+      </c>
+      <c r="M155" t="n">
+        <v>39</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>45674</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>7 ( PESO SECO)</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="R155" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="S155" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="T155" t="n">
+        <v>81</v>
+      </c>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>TORRES SILVIA</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>DESNUTRICIÓN MARASMO KWASHIORKOR, ANEMIA CRÓNICA, GEA Y TRASTORNOS DEL MEDIO INTERNO EN RESOLUCIÓN</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>FORMULA INDICCADA EN INTERNACION F100</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUELLAR RICARDO ROMERO JUNIOR </t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>70227496</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>SALVADOR MAZZA</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L156" t="n">
+        <v>49</v>
+      </c>
+      <c r="M156" t="n">
+        <v>40</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="O156" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="P156" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="R156" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="S156" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="T156" t="n">
+        <v>74</v>
+      </c>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>ROMERO ELENA</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>DESNTRICION CRONICA REAGUDIZADA  SOSPECHA DE ABANDONO (MALTRATO INFANITIL) IRAB ARS</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>INTERNADA</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>FORMUAL INDICADA EN INTERNACION F100</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ TORRES MARIA LUCIA </t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAG</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>70096596</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA MORA </t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>45235</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L157" t="n">
+        <v>49</v>
+      </c>
+      <c r="M157" t="n">
+        <v>38</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="O157" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P157" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="R157" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="S157" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="T157" t="n">
+        <v>78</v>
+      </c>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORES LUCIA </t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA CALORICA MODERADA, GEA, ANEMIA CRONICA</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNDA </t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>FORMLA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHICHI </t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>125 A 2 M 18 D</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr"/>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ACEVEDO BELEN MARTA LUCIA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DNT  AGUDA</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>59620494</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>POZO EL TIGRE SVE</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>44854</v>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L160" t="n">
+        <v>49</v>
+      </c>
+      <c r="M160" t="n">
+        <v>38</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="O160" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="P160" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>IMC 12,9 -2,38</t>
+        </is>
+      </c>
+      <c r="R160" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="S160" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="T160" t="n">
+        <v>80</v>
+      </c>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>ACEVEDO ROSMARY</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DESNUTRICION AGUDA MODERADA TBC E/E GEA TRASTORNO DEL MEDIO INTERNO </t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADA </t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>FORMULA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA KEYTAN LELVIN EUTICO </t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DNT AGUDA</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>70096717</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>POZO EL TIGRE SVE</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>45265</v>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L161" t="n">
+        <v>51</v>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="O161" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="P161" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="R161" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="S161" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="T161" t="n">
+        <v>74</v>
+      </c>
+      <c r="U161" s="2" t="n">
+        <v>45730</v>
+      </c>
+      <c r="V161" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="W161" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="X161" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>93</v>
+      </c>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>GARCIA PASCUALA</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>DESNUTRICION AGUDA SEVERA TRASTORNO DEL MEDIO INTERNO SEVERO</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>FORMULA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHICHI </t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>GABY ADOLFO BELARDO</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>59760007</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTO LA SIERRA </t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>DERIVACION  A.O ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>45128</v>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L162" t="n">
+        <v>43</v>
+      </c>
+      <c r="M162" t="n">
+        <v>36</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>45712</v>
+      </c>
+      <c r="O162" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P162" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="R162" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="S162" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T162" t="n">
+        <v>80</v>
+      </c>
+      <c r="U162" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="V162" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W162" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="X162" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>SUAREZ BEATRIZ</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DESNUTRICIÓN CALORICA SEVERA CON BAJA TALLA. GEA. TRASTORNO DEL MEDIO INTERNO HIPOKALEMIA, IRAB,ARS</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>FORMULA INDICADA EN INTERNACION F75 F100</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDEZ JOSE NAHUEL </t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DNT CRONICA REAGUDIZADA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>V.O</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>70039478</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTO LA SIERRA </t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>DERIVACION A. O ALTO LA SIERRA</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>45183</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L163" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M163" t="n">
+        <v>39</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>45712</v>
+      </c>
+      <c r="O163" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P163" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="R163" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="S163" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="T163" t="n">
+        <v>86</v>
+      </c>
+      <c r="U163" s="2" t="n">
+        <v>45728</v>
+      </c>
+      <c r="V163" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W163" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="X163" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>99</v>
+      </c>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>FIDELA CIRIACO</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>DESNUTRICION ARMONICA CALORICA LEVE CON RIEGO DE BAJA TALLA,EPILEPSIA E/E, ANEMIA CRONICA MODERADA, DIARREA CRONICA INETRMITENTE, PARASITOSIS INTESTINAL, IRAB ARS</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RECUPERADO NUTRICIONALMENTE </t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORMULA ENTERA 225 CC/TOMA AL 15% </t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIAS RITA MARCELA </t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DNT CRONICA </t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>97251739</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>S.V.E</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>PASE DE SALA DE PEDIATRIA</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>45152</v>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L164" t="n">
+        <v>44</v>
+      </c>
+      <c r="M164" t="n">
+        <v>40</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="O164" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="P164" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="R164" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="S164" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="T164" t="n">
+        <v>102</v>
+      </c>
+      <c r="U164" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="V164" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="W164" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="X164" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>96</v>
+      </c>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASTOR IRENE </t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>DESNUTRICION CRONICA , ANEMIA CRONIC. DISPLASIA BRONCOPULMMONAR E/E. DEFICIENCIA INMUNITARIA PRIMARIA E/E, CARDIOPATIA OCULTA E/E. LACTANTE SIBILANTE, ENFERMEDAD RENAL E/E , DEFICIT DE MICRONUTRIENTES, ARS</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DERIVADA A HPMI </t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>F75 -F100</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLA PEREZ AYLIN DEVORA AYELEN </t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>RBP</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SNG</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>59938636</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>LAPACHO II</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>CONSULTORIO EXTERNO</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>45086</v>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L165" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M165" t="n">
+        <v>41</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>45723</v>
+      </c>
+      <c r="O165" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="P165" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="R165" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="S165" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ LORENA </t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DIARREA CRONICA, TRASTORNOS DEL MEDIO INTERNO, RIESGO NUTRICIONAL, DERMATITIS SEBORREICA, ENTEROPARASITOSIS </t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERNADA </t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>WHICHI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
